--- a/5/search/FY3_Missile2_results/solutions_direction_90.0.xlsx
+++ b/5/search/FY3_Missile2_results/solutions_direction_90.0.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,72 +487,72 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B2" t="n">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6256.090488455686</v>
+      </c>
+      <c r="F2" t="n">
+        <v>253.9381773049295</v>
+      </c>
+      <c r="G2" t="n">
+        <v>700</v>
+      </c>
+      <c r="H2" t="n">
+        <v>6256.090488455686</v>
+      </c>
+      <c r="I2" t="n">
+        <v>253.9381773049295</v>
+      </c>
+      <c r="J2" t="n">
+        <v>700</v>
+      </c>
+      <c r="K2" t="n">
         <v>2</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>24</v>
-      </c>
-      <c r="G2" t="n">
-        <v>700</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>192</v>
-      </c>
-      <c r="J2" t="n">
-        <v>680.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.200000000000003</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90</v>
+        <v>85.5</v>
       </c>
       <c r="B3" t="n">
-        <v>95.2</v>
+        <v>132</v>
       </c>
       <c r="C3" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6248.558415265813</v>
+      </c>
+      <c r="F3" t="n">
+        <v>158.2341132665492</v>
+      </c>
+      <c r="G3" t="n">
+        <v>700</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6258.915015901888</v>
+      </c>
+      <c r="I3" t="n">
+        <v>289.8272013193221</v>
+      </c>
+      <c r="J3" t="n">
+        <v>695.1</v>
+      </c>
+      <c r="K3" t="n">
         <v>2</v>
-      </c>
-      <c r="E3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>46.40000000000009</v>
-      </c>
-      <c r="G3" t="n">
-        <v>700</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>236.8000000000001</v>
-      </c>
-      <c r="J3" t="n">
-        <v>680.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -560,10 +560,10 @@
         <v>90</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>100</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>6000</v>
       </c>
       <c r="F4" t="n">
-        <v>214.4000000000001</v>
+        <v>200</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
@@ -581,13 +581,13 @@
         <v>6000</v>
       </c>
       <c r="I4" t="n">
-        <v>214.4000000000001</v>
+        <v>200</v>
       </c>
       <c r="J4" t="n">
         <v>700</v>
       </c>
       <c r="K4" t="n">
-        <v>2.200000000000003</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -595,10 +595,10 @@
         <v>90</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
@@ -616,13 +616,118 @@
         <v>6000</v>
       </c>
       <c r="I5" t="n">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="J5" t="n">
         <v>680.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.400000000000002</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>90</v>
+      </c>
+      <c r="B6" t="n">
+        <v>114</v>
+      </c>
+      <c r="C6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>192</v>
+      </c>
+      <c r="G6" t="n">
+        <v>700</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>192</v>
+      </c>
+      <c r="J6" t="n">
+        <v>700</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>90</v>
+      </c>
+      <c r="B7" t="n">
+        <v>126</v>
+      </c>
+      <c r="C7" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24</v>
+      </c>
+      <c r="G7" t="n">
+        <v>700</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>276</v>
+      </c>
+      <c r="J7" t="n">
+        <v>680.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>90</v>
+      </c>
+      <c r="B8" t="n">
+        <v>130</v>
+      </c>
+      <c r="C8" t="n">
+        <v>24</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F8" t="n">
+        <v>120</v>
+      </c>
+      <c r="G8" t="n">
+        <v>700</v>
+      </c>
+      <c r="H8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>250</v>
+      </c>
+      <c r="J8" t="n">
+        <v>695.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
